--- a/data/About.xlsx
+++ b/data/About.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10821"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javier/Desktop/tmp/javicond3.github.io/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971175F4-6F68-CD44-99E9-E1A2D91206C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38236772-622C-7246-ABBA-54CC42017496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">Hoja1!$B$1:$Z$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
   <si>
     <t>Año</t>
   </si>
@@ -74,9 +74,6 @@
     <t>Assistant Professor</t>
   </si>
   <si>
-    <t>2024-Today</t>
-  </si>
-  <si>
     <t>2023-2024</t>
   </si>
   <si>
@@ -228,15 +225,31 @@
   </si>
   <si>
     <t>2026-Today</t>
+  </si>
+  <si>
+    <t>Profesor Permanente Laboral</t>
+  </si>
+  <si>
+    <t>Associate Professor</t>
+  </si>
+  <si>
+    <t>2024-2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -352,56 +365,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -710,7 +726,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AC22"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27.5" style="16" customWidth="1"/>
@@ -760,7 +776,7 @@
         <v>2</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I1" s="3"/>
       <c r="J1" s="4"/>
@@ -789,19 +805,19 @@
         <v>5</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>12</v>
+        <v>64</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>62</v>
       </c>
       <c r="F2" s="12" t="s">
         <v>9</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="34" x14ac:dyDescent="0.2">
@@ -809,42 +825,42 @@
         <v>5</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="9" t="s">
-        <v>13</v>
+      <c r="E3" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>9</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" ht="51" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
@@ -852,14 +868,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="10"/>
+        <v>15</v>
+      </c>
       <c r="E5" s="9" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>26</v>
@@ -870,19 +885,20 @@
         <v>5</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="11" t="s">
-        <v>15</v>
+      <c r="D6" s="10"/>
+      <c r="E6" s="9" t="s">
+        <v>13</v>
       </c>
       <c r="F6" s="12" t="s">
         <v>9</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="34" x14ac:dyDescent="0.2">
@@ -890,250 +906,270 @@
         <v>5</v>
       </c>
       <c r="B7" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="34" x14ac:dyDescent="0.2">
+      <c r="A8" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="11">
+      <c r="E8" s="11">
         <v>2018</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="102" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="F8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="102" x14ac:dyDescent="0.2">
+      <c r="A9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="C9" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="51" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="51" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="8" t="s">
+    </row>
+    <row r="11" spans="1:29" ht="85" x14ac:dyDescent="0.2">
+      <c r="A11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H9" s="14" t="s">
+      <c r="E11" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="85" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="14" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="9">
-        <v>2014</v>
-      </c>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:29" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
+      <c r="B12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>40</v>
       </c>
       <c r="E12" s="9">
         <v>2014</v>
       </c>
       <c r="H12" s="13"/>
     </row>
-    <row r="13" spans="1:29" ht="34" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>26</v>
+    <row r="13" spans="1:29" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>44</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2014</v>
       </c>
       <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A14" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="F14" s="12" t="s">
         <v>9</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="21" t="s">
-        <v>49</v>
-      </c>
       <c r="C15" s="21" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>9</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>26</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:29" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>9</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="21" t="s">
+      <c r="E18" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="34" x14ac:dyDescent="0.2">
+      <c r="A19" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="C19" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="E19" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
+      <c r="F19" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B23" s="20"/>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
